--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/findAll-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/findAll-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="143">
   <si>
     <t>Statement: ExerciseRepository.findAll(options?) – returns paginated list. Default only active. Supports search, muscleGroup filter, pagination.</t>
   </si>
@@ -166,6 +166,21 @@
     <t>Ordered by name ASC</t>
   </si>
   <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>Returns total=0</t>
+  </si>
+  <si>
+    <t>EC-8</t>
+  </si>
+  <si>
+    <t>Combined filters</t>
+  </si>
+  <si>
+    <t>Filters by all</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
@@ -292,6 +307,18 @@
     <t>Deadlift before Bench Press</t>
   </si>
   <si>
+    <t>No search match</t>
+  </si>
+  <si>
+    <t>total=0</t>
+  </si>
+  <si>
+    <t>All filters at once</t>
+  </si>
+  <si>
+    <t>Combined filtering success</t>
+  </si>
+  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -377,15 +404,6 @@
   </si>
   <si>
     <t>Returns one item</t>
-  </si>
-  <si>
-    <t>EC-1, EC-3, EC-4</t>
-  </si>
-  <si>
-    <t>Combined filters</t>
-  </si>
-  <si>
-    <t>Filters by all</t>
   </si>
   <si>
     <t>Testing</t>
@@ -1085,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1194,6 +1212,40 @@
         <v>48</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1215,13 +1267,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1229,10 +1281,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1243,7 +1295,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1254,7 +1306,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1262,10 +1314,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1287,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1320,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1331,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1339,10 +1391,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1353,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1364,7 +1416,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1372,10 +1424,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1386,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1397,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1408,7 +1460,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1416,10 +1468,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1430,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1441,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +1519,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>31</v>
@@ -1484,13 +1536,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>37</v>
@@ -1501,13 +1553,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>37</v>
@@ -1518,13 +1570,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>37</v>
@@ -1538,7 +1590,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1554,10 +1606,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>31</v>
@@ -1574,16 +1626,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>37</v>
@@ -1603,7 +1655,7 @@
         <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>37</v>
@@ -1623,7 +1675,7 @@
         <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>37</v>
@@ -1643,7 +1695,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>37</v>
@@ -1660,10 +1712,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>37</v>
@@ -1674,16 +1726,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>37</v>
@@ -1694,16 +1746,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>37</v>
@@ -1717,13 +1769,13 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>37</v>
@@ -1737,13 +1789,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>37</v>
@@ -1757,13 +1809,13 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>37</v>
@@ -1777,13 +1829,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>37</v>
@@ -1797,13 +1849,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>37</v>
@@ -1817,13 +1869,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>37</v>
@@ -1837,13 +1889,13 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>37</v>
@@ -1857,13 +1909,13 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>37</v>
@@ -1877,13 +1929,13 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>37</v>
@@ -1897,13 +1949,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>37</v>
@@ -1917,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>37</v>
@@ -1937,13 +1989,13 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>37</v>
@@ -1957,13 +2009,13 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>37</v>
@@ -1977,13 +2029,13 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>37</v>
@@ -1997,13 +2049,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>113</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>37</v>
@@ -2017,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>37</v>
@@ -2037,13 +2089,13 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>37</v>
@@ -2057,13 +2109,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>37</v>
@@ -2074,18 +2126,38 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2114,16 +2186,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2131,45 +2203,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B3" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2178,19 +2250,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/findAll-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/findAll-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="143">
-  <si>
-    <t>Statement: ExerciseRepository.findAll(options?) – returns paginated list. Default only active. Supports search, muscleGroup filter, pagination.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="135">
+  <si>
+    <t>Statement: ExerciseRepository.findAll(options?) – Returns a paginated list of exercises. Supports optional filtering by search term, muscle group, and active status. Supports pagination via page and pageSize. Results are ordered by name ascending.</t>
   </si>
   <si>
     <t/>
@@ -31,13 +31,13 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: ExerciseListOptions? { search?, muscleGroup?, includeInactive?, page?, pageSize? }</t>
+    <t>Input: options?: ExerciseListOptions { search?, muscleGroup?, includeInactive?, page?, pageSize? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. The exercise table may be empty or contain active and inactive exercises across multiple muscle groups.</t>
   </si>
   <si>
     <t>Results</t>
@@ -49,7 +49,7 @@
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns paginated and filtered results ordered by name ASC.</t>
+    <t>On success: PageResult returned with items matching the applied filters, total reflecting the full count, and items ordered by name ascending.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,46 +64,43 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>No options → active exercises only, items.length: 1, total: 1</t>
+  </si>
+  <si>
     <t>Active filter</t>
   </si>
   <si>
-    <t>includeInactive=false</t>
-  </si>
-  <si>
-    <t>includeInactive=true</t>
-  </si>
-  <si>
-    <t>Search term</t>
-  </si>
-  <si>
-    <t>With search term</t>
-  </si>
-  <si>
-    <t>MuscleGroup</t>
-  </si>
-  <si>
-    <t>With muscleGroup filter</t>
+    <t>includeInactive: false → active only, items.length: 1, items[0] equal to MOCK_EXERCISE</t>
+  </si>
+  <si>
+    <t>includeInactive: true → all exercises, items.length: 2, items contains MOCK_EXERCISE and inactiveExercise</t>
+  </si>
+  <si>
+    <t>Muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: MuscleGroup.BACK → filtered items, items[0].muscleGroup: MuscleGroup.BACK</t>
+  </si>
+  <si>
+    <t>Combined filters</t>
+  </si>
+  <si>
+    <t>search: "Bench", muscleGroup: MuscleGroup.CHEST → items[0].muscleGroup: CHEST and items[0].name contains "Bench"</t>
   </si>
   <si>
     <t>Ordering</t>
   </si>
   <si>
-    <t>Multiple exercises</t>
-  </si>
-  <si>
-    <t>Database result</t>
-  </si>
-  <si>
-    <t>Matches found</t>
-  </si>
-  <si>
-    <t>No matches found</t>
-  </si>
-  <si>
-    <t>Pagination</t>
-  </si>
-  <si>
-    <t>Custom page/pageSize</t>
+    <t>Multiple exercises → items[0].name: "A Exercise", items[1].name: "B Exercise"</t>
+  </si>
+  <si>
+    <t>No filters</t>
+  </si>
+  <si>
+    <t>Empty options object → items.length: 2, total: 2, items contains MOCK_EXERCISE and MOCK_EXERCISE_BACK</t>
   </si>
   <si>
     <t>No TC</t>
@@ -121,64 +118,67 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-6</t>
-  </si>
-  <si>
-    <t>No options, active DB</t>
-  </si>
-  <si>
-    <t>Returns active items</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no options</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0] equal to MOCK_EXERCISE, total: 1</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>options: { includeInactive: false }</t>
+  </si>
+  <si>
     <t>EC-3</t>
   </si>
   <si>
-    <t>search="Bench"</t>
-  </si>
-  <si>
-    <t>Filters by name</t>
+    <t>options: { includeInactive: true }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, items contains MOCK_EXERCISE and inactiveExercise, total: 2</t>
   </si>
   <si>
     <t>EC-4</t>
   </si>
   <si>
-    <t>muscleGroup="CHEST"</t>
-  </si>
-  <si>
-    <t>Filters by muscle</t>
-  </si>
-  <si>
-    <t>EC-2</t>
-  </si>
-  <si>
-    <t>Returns all items</t>
+    <t>options: { muscleGroup: MuscleGroup.BACK }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].muscleGroup: MuscleGroup.BACK, items[0] equal to MOCK_EXERCISE_BACK</t>
   </si>
   <si>
     <t>EC-5</t>
   </si>
   <si>
-    <t>Multiple items</t>
-  </si>
-  <si>
-    <t>Ordered by name ASC</t>
+    <t>options: { search: "Bench", muscleGroup: MuscleGroup.CHEST }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].muscleGroup: MuscleGroup.CHEST, items[0].name contains "Bench"</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>no options, exercises: [exerciseA (name: "A Exercise"), exerciseB (name: "B Exercise")]</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, items[0].name: "A Exercise", items[1].name: "B Exercise"</t>
   </si>
   <si>
     <t>EC-7</t>
   </si>
   <si>
-    <t>Returns total=0</t>
-  </si>
-  <si>
-    <t>EC-8</t>
-  </si>
-  <si>
-    <t>Combined filters</t>
-  </si>
-  <si>
-    <t>Filters by all</t>
+    <t>options: {} (empty object)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, total: 2, items contains MOCK_EXERCISE and MOCK_EXERCISE_BACK</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -187,94 +187,178 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>Search param</t>
-  </si>
-  <si>
-    <t>search = undefined</t>
-  </si>
-  <si>
-    <t>search = ""</t>
-  </si>
-  <si>
-    <t>search = "a"</t>
-  </si>
-  <si>
-    <t>MuscleGroup param</t>
-  </si>
-  <si>
-    <t>muscleGroup = CHEST</t>
-  </si>
-  <si>
-    <t>muscleGroup = SHOULDERS</t>
-  </si>
-  <si>
-    <t>muscleGroup = ARMS</t>
-  </si>
-  <si>
-    <t>muscleGroup = BACK</t>
-  </si>
-  <si>
-    <t>muscleGroup = CORE</t>
-  </si>
-  <si>
-    <t>muscleGroup = LEGS</t>
-  </si>
-  <si>
-    <t>muscleGroup = INVALID</t>
-  </si>
-  <si>
-    <t>Inactive param</t>
-  </si>
-  <si>
-    <t>includeInactive = undefined</t>
-  </si>
-  <si>
-    <t>includeInactive = false</t>
-  </si>
-  <si>
-    <t>includeInactive = true</t>
-  </si>
-  <si>
-    <t>Page param</t>
-  </si>
-  <si>
-    <t>page = undefined</t>
-  </si>
-  <si>
-    <t>page = 0</t>
-  </si>
-  <si>
-    <t>page = 1</t>
-  </si>
-  <si>
-    <t>page = 2</t>
-  </si>
-  <si>
-    <t>PageSize param</t>
-  </si>
-  <si>
-    <t>pageSize = undefined</t>
-  </si>
-  <si>
-    <t>pageSize = 0</t>
-  </si>
-  <si>
-    <t>pageSize = 1</t>
+    <t>Search value</t>
+  </si>
+  <si>
+    <t>search: undefined, search: "" (empty), search: "a" (one char)</t>
+  </si>
+  <si>
+    <t>Muscle group enum</t>
+  </si>
+  <si>
+    <t>MuscleGroup.CHEST (found), MuscleGroup.SHOULDERS (empty), MuscleGroup.ARMS (empty), MuscleGroup.BACK (found), MuscleGroup.CORE (empty), MuscleGroup.LEGS (empty), "INVALID" (empty)</t>
+  </si>
+  <si>
+    <t>includeInactive</t>
+  </si>
+  <si>
+    <t>includeInactive: undefined (active only), includeInactive: false (active only), includeInactive: true (all)</t>
+  </si>
+  <si>
+    <t>Page number</t>
+  </si>
+  <si>
+    <t>page: undefined, page: 0 (first), page: 1 (first), page: 2 (second)</t>
+  </si>
+  <si>
+    <t>Page size</t>
+  </si>
+  <si>
+    <t>pageSize: undefined (default), pageSize: 0 (no items), pageSize: 1 (one item)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Undefined</t>
-  </si>
-  <si>
-    <t>Returns items</t>
-  </si>
-  <si>
-    <t>BVA-2 Empty</t>
-  </si>
-  <si>
-    <t>BVA-3 OneChar</t>
+    <t>BVA-1 (undef)</t>
+  </si>
+  <si>
+    <t>options: { search: undefined }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, total: 2</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>options: { search: "" }</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>options: { search: "a" }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0] equal to MOCK_EXERCISE</t>
+  </si>
+  <si>
+    <t>BVA-2 (CHEST)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: MuscleGroup.CHEST }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].muscleGroup: MuscleGroup.CHEST</t>
+  </si>
+  <si>
+    <t>BVA-2 (SHOULDERS)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: MuscleGroup.SHOULDERS }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 0</t>
+  </si>
+  <si>
+    <t>BVA-2 (ARMS)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: MuscleGroup.ARMS }</t>
+  </si>
+  <si>
+    <t>BVA-2 (BACK)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].muscleGroup: MuscleGroup.BACK</t>
+  </si>
+  <si>
+    <t>BVA-2 (CORE)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: MuscleGroup.CORE }</t>
+  </si>
+  <si>
+    <t>BVA-2 (LEGS)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: MuscleGroup.LEGS }</t>
+  </si>
+  <si>
+    <t>BVA-2 (INVALID)</t>
+  </si>
+  <si>
+    <t>options: { muscleGroup: "INVALID" as MuscleGroup }</t>
+  </si>
+  <si>
+    <t>BVA-3 (undef)</t>
+  </si>
+  <si>
+    <t>options: { includeInactive: undefined }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0].isActive: true</t>
+  </si>
+  <si>
+    <t>BVA-3 (false)</t>
+  </si>
+  <si>
+    <t>BVA-3 (true)</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 2, total: 2, items contains MOCK_EXERCISE and inactiveExercise</t>
+  </si>
+  <si>
+    <t>BVA-4 (undef)</t>
+  </si>
+  <si>
+    <t>options: { page: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-4 (p=0)</t>
+  </si>
+  <si>
+    <t>options: { page: 0 }</t>
+  </si>
+  <si>
+    <t>BVA-4 (p=1)</t>
+  </si>
+  <si>
+    <t>options: { page: 1 }</t>
+  </si>
+  <si>
+    <t>BVA-4 (p=2)</t>
+  </si>
+  <si>
+    <t>options: { page: 2, pageSize: 10 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, items[0] equal to MOCK_EXERCISE_BACK, total: 11</t>
+  </si>
+  <si>
+    <t>BVA-5 (undef)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-5 (s=0)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 0 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 0, total: 2</t>
+  </si>
+  <si>
+    <t>BVA-5 (s=1)</t>
+  </si>
+  <si>
+    <t>options: { pageSize: 1 }</t>
+  </si>
+  <si>
+    <t>PageResult with items.length: 1, total: 2</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -283,42 +367,6 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EC-1</t>
-  </si>
-  <si>
-    <t>Default options (Active only)</t>
-  </si>
-  <si>
-    <t>Items total matches count</t>
-  </si>
-  <si>
-    <t>Filtered results</t>
-  </si>
-  <si>
-    <t>Filtered by group</t>
-  </si>
-  <si>
-    <t>All exercises returned</t>
-  </si>
-  <si>
-    <t>Multiple items in DB</t>
-  </si>
-  <si>
-    <t>Deadlift before Bench Press</t>
-  </si>
-  <si>
-    <t>No search match</t>
-  </si>
-  <si>
-    <t>total=0</t>
-  </si>
-  <si>
-    <t>All filters at once</t>
-  </si>
-  <si>
-    <t>Combined filtering success</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
@@ -334,78 +382,6 @@
     <t>BVA-5</t>
   </si>
   <si>
-    <t>BVA-6</t>
-  </si>
-  <si>
-    <t>BVA-7</t>
-  </si>
-  <si>
-    <t>BVA-8</t>
-  </si>
-  <si>
-    <t>BVA-9</t>
-  </si>
-  <si>
-    <t>BVA-10</t>
-  </si>
-  <si>
-    <t>Returns empty result</t>
-  </si>
-  <si>
-    <t>BVA-11</t>
-  </si>
-  <si>
-    <t>Defaults to active</t>
-  </si>
-  <si>
-    <t>BVA-12</t>
-  </si>
-  <si>
-    <t>Returns active</t>
-  </si>
-  <si>
-    <t>BVA-13</t>
-  </si>
-  <si>
-    <t>Returns all</t>
-  </si>
-  <si>
-    <t>BVA-14</t>
-  </si>
-  <si>
-    <t>Returns first page</t>
-  </si>
-  <si>
-    <t>BVA-15</t>
-  </si>
-  <si>
-    <t>BVA-16</t>
-  </si>
-  <si>
-    <t>BVA-17</t>
-  </si>
-  <si>
-    <t>page = 2, total=11, size=10</t>
-  </si>
-  <si>
-    <t>Returns second page</t>
-  </si>
-  <si>
-    <t>BVA-18</t>
-  </si>
-  <si>
-    <t>BVA-19</t>
-  </si>
-  <si>
-    <t>Returns zero items</t>
-  </si>
-  <si>
-    <t>BVA-20</t>
-  </si>
-  <si>
-    <t>Returns one item</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -436,7 +412,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-02/EXM-06</t>
+    <t>REPO-15</t>
   </si>
   <si>
     <t>n/a</t>
@@ -961,7 +937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1002,10 +978,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>1</v>
@@ -1016,7 +992,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>19</v>
@@ -1072,26 +1048,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1115,19 +1077,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1135,16 +1097,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1152,16 +1114,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1169,16 +1131,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1186,16 +1148,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1203,16 +1165,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1220,16 +1182,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1246,7 +1208,7 @@
         <v>53</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1257,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1292,10 +1254,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1303,10 +1265,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1314,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1325,175 +1287,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
         <v>65</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1504,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1516,19 +1313,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1536,16 +1333,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1553,16 +1350,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1570,16 +1367,305 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>37</v>
+      <c r="C9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1603,22 +1689,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1626,19 +1712,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1646,19 +1732,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1666,19 +1752,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1686,19 +1772,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1706,19 +1792,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,19 +1812,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1752,13 +1838,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1769,16 +1855,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1789,16 +1875,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1809,16 +1895,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1829,16 +1915,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1849,16 +1935,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1869,16 +1955,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1889,16 +1975,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1909,16 +1995,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1929,16 +2015,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1949,16 +2035,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1969,16 +2055,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1989,16 +2075,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2009,16 +2095,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2029,16 +2115,16 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2052,13 +2138,13 @@
         <v>119</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="F23" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2069,16 +2155,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2089,16 +2175,16 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2109,16 +2195,16 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2129,16 +2215,16 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2149,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2186,16 +2272,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2203,39 +2289,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="B3" s="1">
         <v>27</v>
@@ -2250,19 +2336,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
